--- a/dev/examples/results/output_file_CO.xlsx
+++ b/dev/examples/results/output_file_CO.xlsx
@@ -553,7 +553,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>3.506913900375366</v>
+        <v>3.5052382946014404</v>
       </c>
       <c r="B2">
         <v>1</v>

--- a/dev/examples/results/output_file_CO.xlsx
+++ b/dev/examples/results/output_file_CO.xlsx
@@ -553,7 +553,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>3.5052382946014404</v>
+        <v>3.61674165725708</v>
       </c>
       <c r="B2">
         <v>1</v>
